--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">short_hand</t>
   </si>
@@ -82,25 +82,28 @@
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
+    <t xml:space="preserve">Hamm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Curiam</t>
+  </si>
+  <si>
     <t xml:space="preserve">First Choice</t>
   </si>
   <si>
-    <t xml:space="preserve">Villarreal</t>
+    <t xml:space="preserve">mean_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
   </si>
   <si>
     <t xml:space="preserve">Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
   </si>
 </sst>
 </file>
@@ -653,39 +656,39 @@
         <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46141</v>
+        <v>46163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45936</v>
+        <v>45993</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46078</v>
+        <v>46141</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +776,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B10" t="n">
         <v>114.75</v>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">short_hand</t>
   </si>
@@ -34,76 +34,73 @@
     <t xml:space="preserve">date_decided</t>
   </si>
   <si>
+    <t xml:space="preserve">Hikma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(9-0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AT\&amp;T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(8-1)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jules</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
   </si>
   <si>
-    <t xml:space="preserve">(9-0)</t>
+    <t xml:space="preserve">Sripetch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
   </si>
   <si>
     <t xml:space="preserve">Galette</t>
   </si>
   <si>
-    <t xml:space="preserve">Enbridge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montgomery</t>
+    <t xml:space="preserve">Fernandez</t>
   </si>
   <si>
     <t xml:space="preserve">Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Coney Island Auto</t>
+    <t xml:space="preserve">Rutherford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callais</t>
   </si>
   <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chiles</t>
   </si>
   <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(8-1)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hencely</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Per Curiam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Choice</t>
-  </si>
-  <si>
     <t xml:space="preserve">mean_elapsed</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kagan</t>
   </si>
   <si>
     <t xml:space="preserve">Kavanaugh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jackson</t>
   </si>
 </sst>
 </file>
@@ -465,7 +462,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -474,10 +471,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46111</v>
+        <v>46141</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46156</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="3">
@@ -485,79 +482,79 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46036</v>
+        <v>46133</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46085</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46079</v>
+        <v>46111</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46134</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B5" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46085</v>
+        <v>46132</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46156</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45965</v>
+        <v>46036</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46042</v>
+        <v>46085</v>
       </c>
     </row>
   </sheetData>
@@ -593,82 +590,82 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46141</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45937</v>
+        <v>45973</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46112</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="n">
+        <v>197</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" t="n">
-        <v>171</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
       <c r="E4" s="1" t="n">
-        <v>45964</v>
+        <v>45945</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46134</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46001</v>
+        <v>45937</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46163</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="6">
@@ -676,19 +673,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45993</v>
+        <v>45964</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46141</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>
@@ -707,20 +704,20 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>103.5</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3" t="n">
         <v>122</v>
@@ -728,7 +725,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B4" t="n">
         <v>137.5</v>
@@ -736,7 +733,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>70.6</v>
@@ -747,15 +744,15 @@
         <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>102.67</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="8">
@@ -763,23 +760,23 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>89.5</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>114.75</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -85,16 +85,16 @@
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
+    <t xml:space="preserve">FS Credit</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chiles</t>
   </si>
   <si>
-    <t xml:space="preserve">Hencely</t>
+    <t xml:space="preserve">mean_elapsed</t>
   </si>
   <si>
     <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mean_elapsed</t>
   </si>
   <si>
     <t xml:space="preserve">Kagan</t>
@@ -653,19 +653,19 @@
         <v>23</v>
       </c>
       <c r="B5" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45937</v>
+        <v>46001</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46112</v>
+        <v>46184</v>
       </c>
     </row>
     <row r="6">
@@ -673,19 +673,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45964</v>
+        <v>45937</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46134</v>
+        <v>46112</v>
       </c>
     </row>
   </sheetData>
@@ -704,7 +704,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -717,7 +717,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" t="n">
         <v>122</v>
@@ -768,7 +768,7 @@
         <v>18</v>
       </c>
       <c r="B9" t="n">
-        <v>143.75</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -52,21 +52,27 @@
     <t xml:space="preserve">(8-1)</t>
   </si>
   <si>
+    <t xml:space="preserve">Sripetch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jules</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor</t>
   </si>
   <si>
-    <t xml:space="preserve">Sripetch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gorsuch</t>
-  </si>
-  <si>
     <t xml:space="preserve">Galette</t>
   </si>
   <si>
+    <t xml:space="preserve">Landor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(6-3)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fernandez</t>
   </si>
   <si>
@@ -76,9 +82,6 @@
     <t xml:space="preserve">Rutherford</t>
   </si>
   <si>
-    <t xml:space="preserve">(6-3)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Callais</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">FS Credit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiles</t>
   </si>
   <si>
     <t xml:space="preserve">mean_elapsed</t>
@@ -511,10 +511,10 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46156</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="5">
@@ -531,10 +531,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46132</v>
+        <v>46111</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46177</v>
+        <v>46156</v>
       </c>
     </row>
     <row r="6">
@@ -545,7 +545,7 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -593,19 +593,19 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
       <c r="E2" s="1" t="n">
-        <v>45973</v>
+        <v>45971</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46170</v>
+        <v>46196</v>
       </c>
     </row>
     <row r="3">
@@ -616,10 +616,10 @@
         <v>198</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>45973</v>
@@ -633,39 +633,39 @@
         <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46141</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="n">
+        <v>197</v>
+      </c>
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="n">
-        <v>184</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
       <c r="E5" s="1" t="n">
-        <v>46001</v>
+        <v>45945</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46184</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="6">
@@ -673,19 +673,19 @@
         <v>24</v>
       </c>
       <c r="B6" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45937</v>
+        <v>46001</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46112</v>
+        <v>46184</v>
       </c>
     </row>
   </sheetData>
@@ -720,23 +720,23 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>122</v>
+        <v>112.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="n">
-        <v>137.5</v>
+        <v>117.17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B5" t="n">
-        <v>70.6</v>
+        <v>68.83</v>
       </c>
     </row>
     <row r="6">
@@ -744,15 +744,15 @@
         <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>95.5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>115.8</v>
+        <v>130.57</v>
       </c>
     </row>
     <row r="8">
@@ -760,15 +760,15 @@
         <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>151.8</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -73,6 +73,9 @@
     <t xml:space="preserve">(6-3)</t>
   </si>
   <si>
+    <t xml:space="preserve">Slaughter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fernandez</t>
   </si>
   <si>
@@ -86,9 +89,6 @@
   </si>
   <si>
     <t xml:space="preserve">Alito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FS Credit</t>
   </si>
   <si>
     <t xml:space="preserve">mean_elapsed</t>
@@ -613,33 +613,33 @@
         <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45973</v>
+        <v>45999</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46170</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
         <v>198</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>45973</v>
@@ -653,39 +653,39 @@
         <v>22</v>
       </c>
       <c r="B5" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46141</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="n">
+        <v>197</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" t="n">
-        <v>184</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46001</v>
+        <v>45945</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46184</v>
+        <v>46141</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +712,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="3">
@@ -725,7 +725,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
         <v>117.17</v>
@@ -744,7 +744,7 @@
         <v>27</v>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>92.33</v>
       </c>
     </row>
     <row r="7">
@@ -765,10 +765,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>136</v>
+        <v>130.71</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
+++ b/Stat Reviews/OT25_StatReview/scotusblog_replication/data/days_elapsed.xlsx
@@ -73,6 +73,12 @@
     <t xml:space="preserve">(6-3)</t>
   </si>
   <si>
+    <t xml:space="preserve">NRSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
     <t xml:space="preserve">Slaughter</t>
   </si>
   <si>
@@ -85,22 +91,16 @@
     <t xml:space="preserve">Rutherford</t>
   </si>
   <si>
-    <t xml:space="preserve">Callais</t>
+    <t xml:space="preserve">mean_elapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
   </si>
   <si>
     <t xml:space="preserve">Alito</t>
   </si>
   <si>
-    <t xml:space="preserve">mean_elapsed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thomas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kagan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavanaugh</t>
   </si>
 </sst>
 </file>
@@ -616,36 +616,36 @@
         <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45973</v>
+        <v>45999</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46170</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="5">
@@ -656,10 +656,10 @@
         <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>45973</v>
@@ -670,22 +670,22 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="n">
+        <v>198</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" t="n">
-        <v>197</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
       <c r="D6" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45945</v>
+        <v>45973</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46141</v>
+        <v>46170</v>
       </c>
     </row>
   </sheetData>
@@ -712,7 +712,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>123.2</v>
+        <v>117.83</v>
       </c>
     </row>
     <row r="3">
@@ -725,7 +725,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" t="n">
         <v>117.17</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" t="n">
         <v>92.33</v>
@@ -757,15 +757,15 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>84.75</v>
+        <v>118.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B9" t="n">
         <v>130.71</v>
